--- a/Result/profitability/4513.xlsx
+++ b/Result/profitability/4513.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.41</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.205</v>
+        <v>-0.195</v>
       </c>
       <c r="N2" t="n">
-        <v>22.7775</v>
+        <v>20.96375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.155</v>
+        <v>-0.15</v>
       </c>
       <c r="N3" t="n">
-        <v>23.1925</v>
+        <v>21.46125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.10625</v>
+        <v>-0.05500000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>23.59125</v>
+        <v>22.34</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08125000000000002</v>
+        <v>-0.0275</v>
       </c>
       <c r="N5" t="n">
-        <v>24.07625</v>
+        <v>22.4575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0525</v>
+        <v>-0.05125</v>
       </c>
       <c r="N6" t="n">
-        <v>24.12875</v>
+        <v>20.48</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.82</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.14125</v>
+        <v>-0.07499999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>22.405</v>
+        <v>22.3575</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.14625</v>
+        <v>-0.165</v>
       </c>
       <c r="N8" t="n">
-        <v>22.1525</v>
+        <v>20.75375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4513</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>923</v>
+      </c>
+      <c r="D75" t="n">
+        <v>844</v>
+      </c>
+      <c r="E75" t="n">
+        <v>79</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.26875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.5662955465587045</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8113207547169812</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-12.95</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6017657992565055</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
